--- a/src/assets/files/sample_upload_milestones_with_tasks_in_project.xlsx
+++ b/src/assets/files/sample_upload_milestones_with_tasks_in_project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehab.zafar\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89CE42C-FA92-4572-A599-3E1C11F1E5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725E9EDE-51EE-435B-BB9D-2775B742BD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>high</t>
   </si>
@@ -76,16 +76,31 @@
     <t>Milestone 1</t>
   </si>
   <si>
-    <t>Task 1</t>
-  </si>
-  <si>
-    <t>Task 2</t>
-  </si>
-  <si>
     <t>rehab.zafar@srl.com.pk</t>
   </si>
   <si>
-    <t>rehab.zafar@srl.com.pk, bilal.iqbal@srl.com.pk</t>
+    <t>task_teams</t>
+  </si>
+  <si>
+    <t>cloud team, D365</t>
+  </si>
+  <si>
+    <t>Task 9</t>
+  </si>
+  <si>
+    <t>Task 10</t>
+  </si>
+  <si>
+    <t>task_status</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>in_progress</t>
+  </si>
+  <si>
+    <t>rehab.zafar@srl.com.pk, bilal.iqbal@srl.com.pk, kinza.amjad@srl.com.pk</t>
   </si>
 </sst>
 </file>
@@ -153,13 +168,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -499,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -507,13 +523,18 @@
     <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="61.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.33203125" customWidth="1"/>
+    <col min="14" max="14" width="20.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -539,19 +560,25 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -568,28 +595,34 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3">
+        <v>21</v>
+      </c>
+      <c r="G2" s="4">
         <v>45597</v>
       </c>
-      <c r="H2" s="3">
-        <v>45598</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2" s="4">
+        <v>45598.083333333336</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -606,172 +639,199 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="3">
+        <v>22</v>
+      </c>
+      <c r="G3" s="4">
         <v>45597</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <v>45598</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I4" s="3"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I5" s="3"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I6" s="3"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I7" s="3"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I8" s="3"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I9" s="3"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I10" s="3"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I11" s="3"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I12" s="3"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I13" s="3"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I14" s="3"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I15" s="3"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I16" s="3"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I17" s="3"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I18" s="3"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I19" s="3"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I20" s="3"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I21" s="3"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I22" s="3"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="J23" s="2"/>
+      <c r="I23" s="3"/>
+      <c r="K23" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" display="rehab.zafar@srl.com.pk" xr:uid="{B2982C5F-F53E-4DB8-9851-605E06CD3C21}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{EE8B2673-6073-4CA6-88F8-74FA5A7AADF3}"/>
+    <hyperlink ref="K2" r:id="rId1" display="rehab.zafar@srl.com.pk" xr:uid="{B2982C5F-F53E-4DB8-9851-605E06CD3C21}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{EE8B2673-6073-4CA6-88F8-74FA5A7AADF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>